--- a/test-data/Templates/SHS/M3 - Create Material type HAWA (N.I).xlsx
+++ b/test-data/Templates/SHS/M3 - Create Material type HAWA (N.I).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejavathidoddapaneni/Maextro_AutomationApp/test-data/Templates/SHS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2A7E1D-2A78-864C-9FC6-DAC980623DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6D7873-B458-F942-A68B-332CF4EB38F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="15140" windowHeight="17180" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
   </bookViews>
   <sheets>
     <sheet name="MXT_HDR" sheetId="1" r:id="rId1"/>
@@ -1296,9 +1296,6 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D6:D13" xr:uid="{58227CB0-C6D9-A247-A15C-D0FCE8718EAF}">
-      <formula1>"Save,Skip,Approve,Reject -&gt; Approve"</formula1>
-    </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{480D1B17-2E92-9240-8BCE-1DA3147CCDB2}">
       <formula1>"New Material"</formula1>
     </dataValidation>
@@ -1307,6 +1304,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{867B6D3F-F6EA-6D45-89A3-70B9CE3A4229}">
       <formula1>"Low,Medium,High"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D6:D13" xr:uid="{6EDD2C76-39B8-0240-9054-C2F0FBA93113}">
+      <formula1>"Save,Skip,Approve,Skip -&gt; Save,Skip -&gt; Approve,Reject -&gt; Approve"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
